--- a/Excel Template.xlsx
+++ b/Excel Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas\Documents\Repetierer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timow\Desktop\Projekte\Repetierer\Repetierer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9E0598-6457-4E5A-8DF2-8C8E54DF8443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A441609-A193-4C07-8056-C24A578FA0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="20186" windowHeight="12800" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="15466" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Class 1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="37">
   <si>
     <t>repetierer</t>
   </si>
@@ -502,404 +502,224 @@
       </c>
     </row>
     <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="I11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
     </row>
     <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="I12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
     </row>
     <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="I13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
     </row>
     <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-      <c r="I14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-      <c r="I15" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
     </row>
     <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-      <c r="I16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
-      <c r="I17" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
-      <c r="I18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
-      <c r="I19" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
-      <c r="I20" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
-      <c r="I21" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
-      <c r="I22" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-      <c r="I23" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
-      <c r="I24" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A25" t="s">
-        <v>24</v>
-      </c>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="I25" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A26" t="s">
-        <v>25</v>
-      </c>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
-      <c r="I26" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A27" t="s">
-        <v>26</v>
-      </c>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="I27" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A28" t="s">
-        <v>27</v>
-      </c>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="I28" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A29" t="s">
-        <v>28</v>
-      </c>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="I29" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A30" t="s">
-        <v>29</v>
-      </c>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="I30" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
@@ -1465,23 +1285,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
@@ -2047,23 +1867,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>

--- a/Excel Template.xlsx
+++ b/Excel Template.xlsx
@@ -1,39 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timow\Desktop\Projekte\Repetierer\Repetierer\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A441609-A193-4C07-8056-C24A578FA0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="15466" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="15466"/>
   </bookViews>
   <sheets>
-    <sheet name="Class 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Class 2" sheetId="2" r:id="rId2"/>
-    <sheet name="Class 3" sheetId="3" r:id="rId3"/>
+    <sheet sheetId="1" name="Class 1" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Class 2" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Class 3" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -55,6 +33,27 @@
     <t>Rounded</t>
   </si>
   <si>
+    <t>Date 1</t>
+  </si>
+  <si>
+    <t>Date 2</t>
+  </si>
+  <si>
+    <t>Date 3</t>
+  </si>
+  <si>
+    <t>Date 4</t>
+  </si>
+  <si>
+    <t>Date 5</t>
+  </si>
+  <si>
+    <t>Date 6</t>
+  </si>
+  <si>
+    <t>Joker Date</t>
+  </si>
+  <si>
     <t>Name 1</t>
   </si>
   <si>
@@ -128,47 +127,26 @@
   </si>
   <si>
     <t>Name 25</t>
-  </si>
-  <si>
-    <t>Joker Date</t>
-  </si>
-  <si>
-    <t>Date 1</t>
-  </si>
-  <si>
-    <t>Date 2</t>
-  </si>
-  <si>
-    <t>Date 3</t>
-  </si>
-  <si>
-    <t>Date 4</t>
-  </si>
-  <si>
-    <t>Date 5</t>
-  </si>
-  <si>
-    <t>Date 6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
+      <charset val="1"/>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -191,17 +169,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -325,90 +300,90 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.703125" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.35" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.5" defaultColWidth="10.703125" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" ht="15.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2">
+    <row r="3" ht="13.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>3</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>4</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>5</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>6</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-    </row>
-    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="K3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" ht="13.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -416,18 +391,19 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="I6" s="1" t="str">
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
         <f t="shared" ref="I6:I30" si="0">IF(COUNT(B6:G6)=0,"",SUM(B6:G6)/COUNT(B6:G6))</f>
-        <v/>
-      </c>
-      <c r="J6" s="1" t="str">
+      </c>
+      <c r="J6" s="1">
         <f t="shared" ref="J6:J30" si="1">IF(COUNT(B6:G6)=0,"",ROUND(I6,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -435,18 +411,19 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="I7" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J7" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -454,18 +431,19 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="I8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J8" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -473,18 +451,19 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="I9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -492,325 +471,386 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="I10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J10" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
+      <c r="H11">
+        <v>1</v>
+      </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="12" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
+      <c r="H12">
+        <v>1</v>
+      </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="13" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
+      <c r="H13">
+        <v>1</v>
+      </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="14" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
+      <c r="H14">
+        <v>1</v>
+      </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="15" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
+      <c r="H15">
+        <v>1</v>
+      </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="16" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
+      <c r="H16">
+        <v>1</v>
+      </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="17" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
+      <c r="H17">
+        <v>1</v>
+      </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="18" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
+      <c r="H18">
+        <v>1</v>
+      </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="19" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
+      <c r="H19">
+        <v>1</v>
+      </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="20" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
+      <c r="H20">
+        <v>1</v>
+      </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="21" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
+      <c r="H21">
+        <v>1</v>
+      </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="22" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
+      <c r="H22">
+        <v>1</v>
+      </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
     </row>
-    <row r="23" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="23" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
+      <c r="H23">
+        <v>1</v>
+      </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
     </row>
-    <row r="24" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="24" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
+      <c r="H24">
+        <v>1</v>
+      </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
     </row>
-    <row r="25" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="25" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
+      <c r="H25">
+        <v>1</v>
+      </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
     </row>
-    <row r="26" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="26" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
+      <c r="H26">
+        <v>1</v>
+      </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
     </row>
-    <row r="27" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="27" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
+      <c r="H27">
+        <v>1</v>
+      </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
     </row>
-    <row r="28" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="28" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
+      <c r="H28">
+        <v>1</v>
+      </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
     </row>
-    <row r="29" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="29" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
+      <c r="H29">
+        <v>1</v>
+      </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
-    <row r="30" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="30" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
+      <c r="H30">
+        <v>1</v>
+      </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="J3:J4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="K3:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.703125" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.35" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.5" defaultColWidth="10.703125" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" ht="15.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2">
+    <row r="3" ht="13.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>3</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>4</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>5</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>6</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-    </row>
-    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="K3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" ht="13.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -818,18 +858,19 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="I6" s="1" t="str">
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
         <f t="shared" ref="I6:I30" si="0">IF(COUNT(B6:G6)=0,"",SUM(B6:G6)/COUNT(B6:G6))</f>
-        <v/>
-      </c>
-      <c r="J6" s="1" t="str">
+      </c>
+      <c r="J6" s="1">
         <f t="shared" ref="J6:J30" si="1">IF(COUNT(B6:G6)=0,"",ROUND(I6,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -837,18 +878,19 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="I7" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J7" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -856,18 +898,19 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="I8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J8" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -875,18 +918,19 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="I9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -894,18 +938,19 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="I10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J10" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -913,18 +958,19 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="I11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J11" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -932,18 +978,19 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="I12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J12" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -951,18 +998,19 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="I13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J13" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -970,18 +1018,19 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-      <c r="I14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J14" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -989,18 +1038,19 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-      <c r="I15" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J15" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1008,18 +1058,19 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-      <c r="I16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J16" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1027,18 +1078,19 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
-      <c r="I17" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J17" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1046,18 +1098,19 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
-      <c r="I18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J18" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1065,18 +1118,19 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
-      <c r="I19" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J19" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1084,18 +1138,19 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
-      <c r="I20" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J20" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1103,18 +1158,19 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
-      <c r="I21" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J21" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1122,18 +1178,19 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
-      <c r="I22" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J22" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1141,18 +1198,19 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-      <c r="I23" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J23" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1160,18 +1218,19 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
-      <c r="I24" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J24" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1179,18 +1238,19 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="I25" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J25" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1198,18 +1258,19 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
-      <c r="I26" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J26" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1217,18 +1278,19 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="I27" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J27" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1236,18 +1298,19 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="I28" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J28" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1255,18 +1318,19 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="I29" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J29" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1274,125 +1338,126 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="I30" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J30" s="1">
+        <f t="shared" si="1"/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="J3:J4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="K3:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.703125" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.35" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.5" defaultColWidth="10.703125" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" ht="15.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2">
+    <row r="3" ht="13.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>3</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>4</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>5</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>6</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-    </row>
-    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="K3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" ht="13.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1400,18 +1465,19 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="I6" s="1" t="str">
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
         <f t="shared" ref="I6:I30" si="0">IF(COUNT(B6:G6)=0,"",SUM(B6:G6)/COUNT(B6:G6))</f>
-        <v/>
-      </c>
-      <c r="J6" s="1" t="str">
+      </c>
+      <c r="J6" s="1">
         <f t="shared" ref="J6:J30" si="1">IF(COUNT(B6:G6)=0,"",ROUND(I6,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1419,18 +1485,19 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="I7" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J7" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1438,18 +1505,19 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="I8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J8" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1457,18 +1525,19 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="I9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1476,18 +1545,19 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="I10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J10" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1495,18 +1565,19 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="I11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J11" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1514,18 +1585,19 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="I12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J12" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1533,18 +1605,19 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="I13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J13" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1552,18 +1625,19 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-      <c r="I14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J14" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1571,18 +1645,19 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-      <c r="I15" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J15" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1590,18 +1665,19 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-      <c r="I16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J16" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1609,18 +1685,19 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
-      <c r="I17" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J17" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1628,18 +1705,19 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
-      <c r="I18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J18" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1647,18 +1725,19 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
-      <c r="I19" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J19" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1666,18 +1745,19 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
-      <c r="I20" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J20" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1685,18 +1765,19 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
-      <c r="I21" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J21" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1704,18 +1785,19 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
-      <c r="I22" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J22" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1723,18 +1805,19 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-      <c r="I23" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J23" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1742,18 +1825,19 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
-      <c r="I24" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J24" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1761,18 +1845,19 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="I25" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J25" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1780,18 +1865,19 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
-      <c r="I26" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J26" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1799,18 +1885,19 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="I27" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J27" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1818,18 +1905,19 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="I28" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J28" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1837,18 +1925,19 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="I29" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J29" s="1">
+        <f t="shared" si="1"/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1856,36 +1945,37 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="I30" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30" s="1">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J30" s="1">
+        <f t="shared" si="1"/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="J3:J4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="K3:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>